--- a/output/pdf_financials_xlsx/EFN.xlsx
+++ b/output/pdf_financials_xlsx/EFN.xlsx
@@ -556,20 +556,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>47.398</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>135.262</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>298.868</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>422.372</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>663.76</v>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
@@ -618,44 +628,70 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>3.269</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>16.156</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>49.525</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>140.383</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>175.978</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>348.468</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>377.091</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>451.779</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>497.521</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>192.869</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>272.835</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>430.773</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>553.324</v>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -1389,19 +1425,19 @@
         <v>0</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0</v>
+        <v>47.398</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0</v>
+        <v>135.262</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0</v>
+        <v>298.868</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0</v>
+        <v>422.372</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0</v>
+        <v>663.76</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>0</v>
@@ -2230,19 +2266,19 @@
         <v>-7.544</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>-11.37</v>
+        <v>-58.768</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>4.846</v>
+        <v>-130.416</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>58.168</v>
+        <v>-240.7</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>157.682</v>
+        <v>-264.69</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>413.021</v>
+        <v>-250.739</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>174.719</v>
@@ -2332,19 +2368,19 @@
         <v>-7.394</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-10.787</v>
+        <v>-58.185</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>5.312</v>
+        <v>-129.95</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>59.11</v>
+        <v>-239.758</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>157.682</v>
+        <v>-264.69</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>424.098</v>
+        <v>-239.662</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>190.695</v>
@@ -2383,7 +2419,7 @@
         <v>-122.013201320132</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>-31.37397475423186</v>
+        <v>-169.2309929614333</v>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
@@ -2401,7 +2437,7 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>42.47946632477262</v>
+        <v>-24.00556913337874</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>20.03041930533483</v>
@@ -2980,75 +3016,47 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>4.116</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>9.997</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>12.401</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>66.869</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>56.764</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>12.638</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>76.637</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>21.999</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>24.224</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>45.271</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>68.876</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>50.85</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>96.419</v>
       </c>
     </row>
     <row r="47">
@@ -3134,75 +3142,47 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>4.116</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>9.997</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>12.401</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>66.869</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>56.764</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>12.638</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>76.637</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>21.999</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>24.224</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>45.271</v>
+      </c>
+      <c r="M48" s="3" t="n">
+        <v>68.876</v>
+      </c>
+      <c r="N48" s="3" t="n">
+        <v>50.85</v>
+      </c>
+      <c r="O48" s="3" t="n">
+        <v>96.419</v>
       </c>
     </row>
     <row r="49">
@@ -9939,7 +9919,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11391,7 +11371,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -17407,7 +17387,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
@@ -42001,7 +41981,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -49861,7 +49841,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -50103,7 +50083,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -53729,7 +53709,7 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
@@ -55447,7 +55427,7 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">

--- a/output/pdf_financials_xlsx/EFN.xlsx
+++ b/output/pdf_financials_xlsx/EFN.xlsx
@@ -7937,16 +7937,16 @@
         </is>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.583</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.466</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -33895,7 +33895,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -36255,7 +36255,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -38275,7 +38275,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">

--- a/output/pdf_financials_xlsx/EFN.xlsx
+++ b/output/pdf_financials_xlsx/EFN.xlsx
@@ -8753,31 +8753,31 @@
         </is>
       </c>
       <c r="C131" s="3" t="n">
-        <v>0</v>
+        <v>-0.093</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>0</v>
+        <v>-0.354</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>0</v>
+        <v>-16.689</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>0</v>
+        <v>-6.081</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>0</v>
+        <v>-17.574</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>0</v>
+        <v>-38.77</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>0</v>
+        <v>-47.05</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>0</v>
+        <v>-36.269</v>
       </c>
       <c r="K131" s="3" t="n">
-        <v>0</v>
+        <v>-26.314</v>
       </c>
       <c r="L131" s="3" t="n">
         <v>0</v>
@@ -9028,7 +9028,7 @@
         <v>0</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>0</v>
+        <v>-78.917</v>
       </c>
       <c r="J136" s="3" t="n">
         <v>0</v>
@@ -9037,16 +9037,16 @@
         <v>0</v>
       </c>
       <c r="L136" s="3" t="n">
-        <v>0</v>
+        <v>-532.336</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>0</v>
+        <v>-196.17</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>0</v>
+        <v>-54.578</v>
       </c>
       <c r="O136" s="3" t="n">
-        <v>0</v>
+        <v>-10.85</v>
       </c>
     </row>
     <row r="137">
@@ -21221,7 +21221,11 @@
           <t>Shares repurchased (note 12)</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -23089,7 +23093,11 @@
           <t>Shares repurchased (note 11)</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -25797,7 +25805,11 @@
           <t>Purchase of intangible assets (note 9)</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -27159,7 +27171,11 @@
           <t>Shares repurchased</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -28669,7 +28685,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -29079,7 +29099,11 @@
           <t>Shares repurchased</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -33041,7 +33065,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -35403,7 +35431,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -37345,7 +37377,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>
